--- a/artfynd/A 43230-2024 artfynd.xlsx
+++ b/artfynd/A 43230-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123325374</v>
       </c>
       <c r="B2" t="n">
-        <v>79384</v>
+        <v>79387</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 43230-2024 artfynd.xlsx
+++ b/artfynd/A 43230-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123325374</v>
       </c>
       <c r="B2" t="n">
-        <v>79387</v>
+        <v>79389</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 43230-2024 artfynd.xlsx
+++ b/artfynd/A 43230-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123325374</v>
       </c>
       <c r="B2" t="n">
-        <v>79389</v>
+        <v>79390</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 43230-2024 artfynd.xlsx
+++ b/artfynd/A 43230-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123325374</v>
       </c>
       <c r="B2" t="n">
-        <v>79390</v>
+        <v>79393</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 43230-2024 artfynd.xlsx
+++ b/artfynd/A 43230-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123325374</v>
       </c>
       <c r="B2" t="n">
-        <v>79393</v>
+        <v>79399</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 43230-2024 artfynd.xlsx
+++ b/artfynd/A 43230-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123325374</v>
       </c>
       <c r="B2" t="n">
-        <v>79399</v>
+        <v>79404</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 43230-2024 artfynd.xlsx
+++ b/artfynd/A 43230-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123325374</v>
       </c>
       <c r="B2" t="n">
-        <v>79404</v>
+        <v>79406</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
